--- a/Data Files/promotion.xlsx
+++ b/Data Files/promotion.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15360" windowHeight="6900" tabRatio="500" firstSheet="19" activeTab="19"/>
+    <workbookView windowWidth="15360" windowHeight="7500" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Promo Hemat" sheetId="1" r:id="rId1"/>
